--- a/artfynd/A 65537-2020 artfynd.xlsx
+++ b/artfynd/A 65537-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128325203</v>
       </c>
       <c r="B2" t="n">
-        <v>106769</v>
+        <v>106774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128325205</v>
       </c>
       <c r="B3" t="n">
-        <v>106769</v>
+        <v>106774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128326010</v>
+        <v>128324813</v>
       </c>
       <c r="B4" t="n">
-        <v>106315</v>
+        <v>103935</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,26 +906,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -934,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703360</v>
+        <v>703364</v>
       </c>
       <c r="R4" t="n">
-        <v>6360578</v>
+        <v>6360576</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1005,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128324813</v>
+        <v>128326010</v>
       </c>
       <c r="B5" t="n">
-        <v>103930</v>
+        <v>106320</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,22 +1012,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703364</v>
+        <v>703360</v>
       </c>
       <c r="R5" t="n">
-        <v>6360576</v>
+        <v>6360578</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>

--- a/artfynd/A 65537-2020 artfynd.xlsx
+++ b/artfynd/A 65537-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128325203</v>
       </c>
       <c r="B2" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128325205</v>
       </c>
       <c r="B3" t="n">
-        <v>106774</v>
+        <v>106867</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128324813</v>
+        <v>128326010</v>
       </c>
       <c r="B4" t="n">
-        <v>103935</v>
+        <v>106413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,22 +906,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -930,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703364</v>
+        <v>703360</v>
       </c>
       <c r="R4" t="n">
-        <v>6360576</v>
+        <v>6360578</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1001,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128326010</v>
+        <v>128324813</v>
       </c>
       <c r="B5" t="n">
-        <v>106320</v>
+        <v>104028</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,26 +1016,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703360</v>
+        <v>703364</v>
       </c>
       <c r="R5" t="n">
-        <v>6360578</v>
+        <v>6360576</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>

--- a/artfynd/A 65537-2020 artfynd.xlsx
+++ b/artfynd/A 65537-2020 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128326010</v>
+        <v>128324813</v>
       </c>
       <c r="B4" t="n">
-        <v>106413</v>
+        <v>104028</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,26 +906,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -934,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703360</v>
+        <v>703364</v>
       </c>
       <c r="R4" t="n">
-        <v>6360578</v>
+        <v>6360576</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1005,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128324813</v>
+        <v>128326010</v>
       </c>
       <c r="B5" t="n">
-        <v>104028</v>
+        <v>106413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,22 +1012,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703364</v>
+        <v>703360</v>
       </c>
       <c r="R5" t="n">
-        <v>6360576</v>
+        <v>6360578</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>

--- a/artfynd/A 65537-2020 artfynd.xlsx
+++ b/artfynd/A 65537-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128325203</v>
       </c>
       <c r="B2" t="n">
-        <v>106867</v>
+        <v>106890</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128325205</v>
       </c>
       <c r="B3" t="n">
-        <v>106867</v>
+        <v>106890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128324813</v>
+        <v>128326010</v>
       </c>
       <c r="B4" t="n">
-        <v>104028</v>
+        <v>106435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,22 +906,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -930,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703364</v>
+        <v>703360</v>
       </c>
       <c r="R4" t="n">
-        <v>6360576</v>
+        <v>6360578</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1001,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128326010</v>
+        <v>128324813</v>
       </c>
       <c r="B5" t="n">
-        <v>106413</v>
+        <v>104049</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,26 +1016,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703360</v>
+        <v>703364</v>
       </c>
       <c r="R5" t="n">
-        <v>6360578</v>
+        <v>6360576</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>

--- a/artfynd/A 65537-2020 artfynd.xlsx
+++ b/artfynd/A 65537-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128325203</v>
       </c>
       <c r="B2" t="n">
-        <v>106890</v>
+        <v>106902</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128325205</v>
       </c>
       <c r="B3" t="n">
-        <v>106890</v>
+        <v>106902</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128326010</v>
+        <v>128324813</v>
       </c>
       <c r="B4" t="n">
-        <v>106435</v>
+        <v>104061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,26 +906,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -934,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703360</v>
+        <v>703364</v>
       </c>
       <c r="R4" t="n">
-        <v>6360578</v>
+        <v>6360576</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1005,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128324813</v>
+        <v>128326010</v>
       </c>
       <c r="B5" t="n">
-        <v>104049</v>
+        <v>106447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,22 +1012,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703364</v>
+        <v>703360</v>
       </c>
       <c r="R5" t="n">
-        <v>6360576</v>
+        <v>6360578</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>

--- a/artfynd/A 65537-2020 artfynd.xlsx
+++ b/artfynd/A 65537-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128325203</v>
       </c>
       <c r="B2" t="n">
-        <v>106902</v>
+        <v>106911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128325205</v>
       </c>
       <c r="B3" t="n">
-        <v>106902</v>
+        <v>106911</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128324813</v>
+        <v>128326010</v>
       </c>
       <c r="B4" t="n">
-        <v>104061</v>
+        <v>106456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,22 +906,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -930,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703364</v>
+        <v>703360</v>
       </c>
       <c r="R4" t="n">
-        <v>6360576</v>
+        <v>6360578</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1001,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128326010</v>
+        <v>128324813</v>
       </c>
       <c r="B5" t="n">
-        <v>106447</v>
+        <v>104070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,26 +1016,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703360</v>
+        <v>703364</v>
       </c>
       <c r="R5" t="n">
-        <v>6360578</v>
+        <v>6360576</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>

--- a/artfynd/A 65537-2020 artfynd.xlsx
+++ b/artfynd/A 65537-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128325203</v>
       </c>
       <c r="B2" t="n">
-        <v>106911</v>
+        <v>106916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128325205</v>
       </c>
       <c r="B3" t="n">
-        <v>106911</v>
+        <v>106916</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128326010</v>
+        <v>128324813</v>
       </c>
       <c r="B4" t="n">
-        <v>106456</v>
+        <v>104073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,26 +906,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -934,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703360</v>
+        <v>703364</v>
       </c>
       <c r="R4" t="n">
-        <v>6360578</v>
+        <v>6360576</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1005,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128324813</v>
+        <v>128326010</v>
       </c>
       <c r="B5" t="n">
-        <v>104070</v>
+        <v>106461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,22 +1012,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703364</v>
+        <v>703360</v>
       </c>
       <c r="R5" t="n">
-        <v>6360576</v>
+        <v>6360578</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>

--- a/artfynd/A 65537-2020 artfynd.xlsx
+++ b/artfynd/A 65537-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128325203</v>
       </c>
       <c r="B2" t="n">
-        <v>106916</v>
+        <v>106944</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128325205</v>
       </c>
       <c r="B3" t="n">
-        <v>106916</v>
+        <v>106944</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128324813</v>
       </c>
       <c r="B4" t="n">
-        <v>104073</v>
+        <v>104100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>128326010</v>
       </c>
       <c r="B5" t="n">
-        <v>106461</v>
+        <v>106489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 65537-2020 artfynd.xlsx
+++ b/artfynd/A 65537-2020 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128324813</v>
+        <v>128326010</v>
       </c>
       <c r="B4" t="n">
-        <v>104100</v>
+        <v>106489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,22 +906,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -930,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703364</v>
+        <v>703360</v>
       </c>
       <c r="R4" t="n">
-        <v>6360576</v>
+        <v>6360578</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1001,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128326010</v>
+        <v>128324813</v>
       </c>
       <c r="B5" t="n">
-        <v>106489</v>
+        <v>104100</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,26 +1016,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703360</v>
+        <v>703364</v>
       </c>
       <c r="R5" t="n">
-        <v>6360578</v>
+        <v>6360576</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>

--- a/artfynd/A 65537-2020 artfynd.xlsx
+++ b/artfynd/A 65537-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128325203</v>
       </c>
       <c r="B2" t="n">
-        <v>106944</v>
+        <v>106957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128325205</v>
       </c>
       <c r="B3" t="n">
-        <v>106944</v>
+        <v>106957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128326010</v>
       </c>
       <c r="B4" t="n">
-        <v>106489</v>
+        <v>106502</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128324813</v>
       </c>
       <c r="B5" t="n">
-        <v>104100</v>
+        <v>104113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 65537-2020 artfynd.xlsx
+++ b/artfynd/A 65537-2020 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128326010</v>
+        <v>128324813</v>
       </c>
       <c r="B4" t="n">
-        <v>106502</v>
+        <v>104113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,26 +906,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -934,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703360</v>
+        <v>703364</v>
       </c>
       <c r="R4" t="n">
-        <v>6360578</v>
+        <v>6360576</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1005,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128324813</v>
+        <v>128326010</v>
       </c>
       <c r="B5" t="n">
-        <v>104113</v>
+        <v>106502</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,22 +1012,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703364</v>
+        <v>703360</v>
       </c>
       <c r="R5" t="n">
-        <v>6360576</v>
+        <v>6360578</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>

--- a/artfynd/A 65537-2020 artfynd.xlsx
+++ b/artfynd/A 65537-2020 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128324813</v>
+        <v>128326010</v>
       </c>
       <c r="B4" t="n">
-        <v>104113</v>
+        <v>106502</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,22 +906,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224416</v>
+        <v>221903</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -930,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703364</v>
+        <v>703360</v>
       </c>
       <c r="R4" t="n">
-        <v>6360576</v>
+        <v>6360578</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1001,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128326010</v>
+        <v>128324813</v>
       </c>
       <c r="B5" t="n">
-        <v>106502</v>
+        <v>104113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,26 +1016,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221903</v>
+        <v>224416</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703360</v>
+        <v>703364</v>
       </c>
       <c r="R5" t="n">
-        <v>6360578</v>
+        <v>6360576</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>

--- a/artfynd/A 65537-2020 artfynd.xlsx
+++ b/artfynd/A 65537-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128325203</v>
       </c>
       <c r="B2" t="n">
-        <v>106957</v>
+        <v>106961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128325205</v>
       </c>
       <c r="B3" t="n">
-        <v>106957</v>
+        <v>106961</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128326010</v>
       </c>
       <c r="B4" t="n">
-        <v>106502</v>
+        <v>106506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>128324813</v>
       </c>
       <c r="B5" t="n">
-        <v>104113</v>
+        <v>104117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
